--- a/PREGAME/1. ELICITACION/1.3 HIstorias de Usuario/GN_Matriz de Marco de Trabajo HU_G2_PintaAuto.xlsx
+++ b/PREGAME/1. ELICITACION/1.3 HIstorias de Usuario/GN_Matriz de Marco de Trabajo HU_G2_PintaAuto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uespe-my.sharepoint.com/personal/dgreinoso_espe_edu_ec/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\6TO SEMESTRE\ANALISIS Y DISEÑO DE SOFTWARE\REPOSITORIO\22426_G2_ADS\PREGAME\1. ELICITACION\1.3 HIstorias de Usuario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5E8C60B-BC0C-4748-AFEF-4CF433CCDCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7937D0F-2AA5-45FF-9515-633BEE6C8E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="110">
   <si>
     <t>Matriz de Marco de Trabajo de HU</t>
   </si>
@@ -358,6 +358,30 @@
   </si>
   <si>
     <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>REQ010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materias primas ya inexistenten en bodega </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quitar aquellas materriales que ya no estan en bodega </t>
+  </si>
+  <si>
+    <t>Para dar de baja a las materias primas que ya no cuentan con stock dentro de bodega y mantener la consistencia del flujo de ingreso y salida de material</t>
+  </si>
+  <si>
+    <t>selecciona la opción eliminar, selecciona la materia prima que desea eliminar</t>
+  </si>
+  <si>
+    <t>El aplicativo muestra un mensaje de confirmación para eliminar la materia prima</t>
+  </si>
+  <si>
+    <t>Eliminar Materia Prima</t>
+  </si>
+  <si>
+    <t>La materia prima debe de estar previamente creada</t>
   </si>
 </sst>
 </file>
@@ -367,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,6 +493,10 @@
       <name val="Arial MT"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -520,7 +548,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -766,11 +794,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -862,19 +905,41 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,30 +966,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,6 +1001,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -952,38 +1016,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1320,8 +1366,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="B1:P1001"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.625" style="15" customWidth="1"/>
     <col min="2" max="2" width="6.625" style="15" customWidth="1"/>
@@ -1348,22 +1394,22 @@
       <c r="L2" s="16"/>
     </row>
     <row r="3" spans="2:16" ht="45" customHeight="1">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="75"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="46"/>
     </row>
     <row r="4" spans="2:16" ht="16.5">
       <c r="I4" s="16"/>
@@ -1587,7 +1633,7 @@
       <c r="N9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="72" t="s">
+      <c r="O9" s="42" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1628,13 +1674,13 @@
       <c r="M10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="70" t="s">
+      <c r="N10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="O10" s="69" t="s">
+      <c r="O10" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="P10" s="71"/>
+      <c r="P10" s="41"/>
     </row>
     <row r="11" spans="2:16" ht="64.5" customHeight="1">
       <c r="B11" s="19" t="s">
@@ -1676,37 +1722,37 @@
       <c r="N11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="73" t="s">
+      <c r="O11" s="43" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="61.5" customHeight="1">
+    <row r="12" spans="2:16" ht="63.75">
       <c r="B12" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>69</v>
+      <c r="C12" s="93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>104</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="23" t="s">
-        <v>71</v>
+      <c r="G12" s="19" t="s">
+        <v>106</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="I12" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" s="20">
-        <v>45450</v>
+        <v>45449</v>
       </c>
       <c r="K12" s="19" t="s">
         <v>32</v>
@@ -1715,33 +1761,33 @@
         <v>23</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="N12" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="O12" s="19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="70.5" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="O12" s="43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="61.5" customHeight="1">
       <c r="B13" s="19" t="s">
         <v>76</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H13" s="19" t="s">
         <v>72</v>
@@ -1750,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="20">
-        <v>45451</v>
+        <v>45450</v>
       </c>
       <c r="K13" s="19" t="s">
         <v>32</v>
@@ -1759,16 +1805,16 @@
         <v>23</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="O13" s="19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" ht="61.5" customHeight="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="70.5" customHeight="1">
       <c r="B14" s="19" t="s">
         <v>83</v>
       </c>
@@ -1776,16 +1822,16 @@
         <v>77</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H14" s="19" t="s">
         <v>72</v>
@@ -1794,7 +1840,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="20">
-        <v>45452</v>
+        <v>45451</v>
       </c>
       <c r="K14" s="19" t="s">
         <v>32</v>
@@ -1803,50 +1849,64 @@
         <v>23</v>
       </c>
       <c r="M14" s="19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="N14" s="19" t="s">
         <v>25</v>
       </c>
       <c r="O14" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="61.5" customHeight="1">
+      <c r="B15" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="19">
+        <v>3</v>
+      </c>
+      <c r="J15" s="20">
+        <v>45452</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="19" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="15" spans="2:16" ht="39.75" customHeight="1">
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-    </row>
-    <row r="16" spans="2:16" ht="39.75" customHeight="1">
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="25"/>
     </row>
     <row r="17" spans="2:15" ht="39.75" customHeight="1">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
@@ -1855,14 +1915,13 @@
       <c r="K17" s="26"/>
       <c r="L17" s="26"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
+      <c r="N17" s="28"/>
       <c r="O17" s="25"/>
     </row>
     <row r="18" spans="2:15" ht="39.75" customHeight="1">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
@@ -1870,7 +1929,7 @@
       <c r="J18" s="27"/>
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
-      <c r="M18" s="28"/>
+      <c r="M18" s="25"/>
       <c r="N18" s="25"/>
       <c r="O18" s="25"/>
     </row>
@@ -1886,17 +1945,27 @@
       <c r="J19" s="27"/>
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
-      <c r="M19" s="25" t="s">
+      <c r="M19" s="28"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+    </row>
+    <row r="20" spans="2:15" ht="39.75" customHeight="1">
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="N19" s="25"/>
-      <c r="O19" s="28"/>
-    </row>
-    <row r="20" spans="2:15" ht="19.5" customHeight="1">
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="16"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="28"/>
     </row>
     <row r="21" spans="2:15" ht="19.5" customHeight="1">
       <c r="I21" s="16"/>
@@ -1905,13 +1974,13 @@
       <c r="L21" s="16"/>
     </row>
     <row r="22" spans="2:15" ht="19.5" customHeight="1">
-      <c r="H22" s="28"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
       <c r="K22" s="17"/>
       <c r="L22" s="16"/>
     </row>
     <row r="23" spans="2:15" ht="19.5" customHeight="1">
+      <c r="H23" s="28"/>
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
       <c r="K23" s="17"/>
@@ -1920,7 +1989,7 @@
     <row r="24" spans="2:15" ht="19.5" customHeight="1">
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
-      <c r="K24" s="29"/>
+      <c r="K24" s="17"/>
       <c r="L24" s="16"/>
     </row>
     <row r="25" spans="2:15" ht="19.5" customHeight="1">
@@ -1932,56 +2001,59 @@
     <row r="26" spans="2:15" ht="19.5" customHeight="1">
       <c r="I26" s="16"/>
       <c r="J26" s="16"/>
-      <c r="K26" s="17"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="16"/>
     </row>
     <row r="27" spans="2:15" ht="19.5" customHeight="1">
       <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="16"/>
     </row>
     <row r="28" spans="2:15" ht="19.5" customHeight="1">
       <c r="I28" s="16"/>
     </row>
     <row r="29" spans="2:15" ht="19.5" customHeight="1">
       <c r="I29" s="16"/>
-      <c r="K29" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" s="17" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="30" spans="2:15" ht="19.5" customHeight="1">
       <c r="I30" s="16"/>
       <c r="K30" s="17" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="L30" s="17" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="19.5" customHeight="1">
       <c r="I31" s="16"/>
       <c r="K31" s="17" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="19.5" customHeight="1">
       <c r="I32" s="16"/>
-      <c r="K32" s="17"/>
+      <c r="K32" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="L32" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="9:12" ht="19.5" customHeight="1">
       <c r="I33" s="16"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="34" spans="9:12" ht="19.5" customHeight="1">
       <c r="I34" s="16"/>
     </row>
-    <row r="35" spans="9:12" ht="15.75" customHeight="1">
+    <row r="35" spans="9:12" ht="19.5" customHeight="1">
       <c r="I35" s="16"/>
     </row>
     <row r="36" spans="9:12" ht="15.75" customHeight="1">
@@ -1989,9 +2061,6 @@
     </row>
     <row r="37" spans="9:12" ht="15.75" customHeight="1">
       <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="16"/>
     </row>
     <row r="38" spans="9:12" ht="15.75" customHeight="1">
       <c r="I38" s="16"/>
@@ -7771,10 +7840,17 @@
       <c r="K1000" s="17"/>
       <c r="L1000" s="16"/>
     </row>
+    <row r="1001" spans="9:12" ht="15.75" customHeight="1">
+      <c r="I1001" s="16"/>
+      <c r="J1001" s="16"/>
+      <c r="K1001" s="17"/>
+      <c r="L1001" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:O3"/>
   </mergeCells>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="L6:L10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -7785,8 +7861,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11:L14">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="L11:L15">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7796,14 +7872,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K15:L19" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K17:L20" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L6:L14" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$L$29:$L$32</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L6:L15" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>$L$30:$L$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K6:K14" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$K$29:$K$31</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K6:K15" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>$K$30:$K$32</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -7818,7 +7894,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:P1020"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
     <col min="2" max="2" width="2.625" customWidth="1"/>
@@ -7842,23 +7918,23 @@
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="2:16" ht="39.75" customHeight="1">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="77"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="2:16" ht="9.75" customHeight="1">
       <c r="C7" s="3"/>
@@ -7898,15 +7974,15 @@
         <v>1</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="77"/>
+      <c r="F9" s="68"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="77"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -7918,20 +7994,20 @@
     <row r="10" spans="2:16" ht="30" customHeight="1">
       <c r="B10" s="37"/>
       <c r="C10" s="7" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="54" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,5,0)</f>
+      <c r="E10" s="70" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,5,0)</f>
         <v>Propietario</v>
       </c>
-      <c r="F10" s="77"/>
+      <c r="F10" s="68"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="54" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,11,0)</f>
+      <c r="H10" s="70" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,11,0)</f>
         <v>No iniciado</v>
       </c>
-      <c r="I10" s="77"/>
+      <c r="I10" s="68"/>
       <c r="J10" s="9"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -7963,15 +8039,15 @@
         <v>95</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="77"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="77"/>
+      <c r="I12" s="68"/>
       <c r="J12" s="9"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -7983,21 +8059,21 @@
     <row r="13" spans="2:16" ht="30" customHeight="1">
       <c r="B13" s="37"/>
       <c r="C13" s="7">
-        <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B6:O19,8,0)</f>
-        <v>2</v>
+        <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B6:O20,8,0)</f>
+        <v>3</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="54" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,10,0)</f>
+      <c r="E13" s="70" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,10,0)</f>
         <v>Alta</v>
       </c>
-      <c r="F13" s="77"/>
+      <c r="F13" s="68"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="54" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,7,0)</f>
-        <v>Ariel Guevara</v>
-      </c>
-      <c r="I13" s="77"/>
+      <c r="H13" s="70" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,7,0)</f>
+        <v>Gabriel Reinoso</v>
+      </c>
+      <c r="I13" s="68"/>
       <c r="J13" s="9"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -8025,68 +8101,68 @@
     </row>
     <row r="15" spans="2:16" ht="19.5" customHeight="1">
       <c r="B15" s="37"/>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="60" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,3,0)</f>
-        <v>Quitar aquellas ordenes que ya se atendieron</v>
-      </c>
-      <c r="E15" s="61"/>
+      <c r="D15" s="75" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,3,0)</f>
+        <v>Generar reporte en fechas especificas</v>
+      </c>
+      <c r="E15" s="76"/>
       <c r="F15" s="30"/>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="60" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,4,0)</f>
-        <v>Para descartar las ordenes de trabajo que ya se atendieron y dar prioridad a las que estan pendientes</v>
-      </c>
-      <c r="I15" s="66"/>
-      <c r="J15" s="61"/>
+      <c r="H15" s="75" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,4,0)</f>
+        <v>Para que tenga una visión clara del inventario durante una fecha especifica</v>
+      </c>
+      <c r="I15" s="83"/>
+      <c r="J15" s="76"/>
       <c r="K15" s="30"/>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="M15" s="43" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,6,0)</f>
-        <v>selecciona la opción eliminar orden de trabajo, selecciona la orden de trabajo que desea eliminar</v>
-      </c>
-      <c r="N15" s="44"/>
-      <c r="O15" s="45"/>
+      <c r="M15" s="86" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,6,0)</f>
+        <v>Selecciona la opcion de generar reportes, ingresa la fecha de la cual quiere el reporte</v>
+      </c>
+      <c r="N15" s="58"/>
+      <c r="O15" s="59"/>
       <c r="P15" s="38"/>
     </row>
     <row r="16" spans="2:16" ht="19.5" customHeight="1">
       <c r="B16" s="37"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="63"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="78"/>
       <c r="F16" s="30"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="63"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="78"/>
       <c r="K16" s="30"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="48"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="60"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="62"/>
       <c r="P16" s="38"/>
     </row>
     <row r="17" spans="2:16" ht="19.5" customHeight="1">
       <c r="B17" s="37"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="65"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
       <c r="F17" s="30"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="65"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="80"/>
       <c r="K17" s="30"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="51"/>
+      <c r="L17" s="82"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="65"/>
       <c r="P17" s="38"/>
     </row>
     <row r="18" spans="2:16" ht="9.75" customHeight="1">
@@ -8108,41 +8184,41 @@
     </row>
     <row r="19" spans="2:16" ht="19.5" customHeight="1">
       <c r="B19" s="37"/>
-      <c r="C19" s="55" t="s">
+      <c r="C19" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="52" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,14,0)</f>
-        <v xml:space="preserve">Eliminar una Orden de Trabajo </v>
-      </c>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="82"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="87" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,14,0)</f>
+        <v>Generar reportes por fechas</v>
+      </c>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="89"/>
       <c r="P19" s="38"/>
     </row>
     <row r="20" spans="2:16" ht="19.5" customHeight="1">
       <c r="B20" s="37"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="87"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="92"/>
       <c r="P20" s="38"/>
     </row>
     <row r="21" spans="2:16" ht="9.75" customHeight="1">
@@ -8164,63 +8240,63 @@
     </row>
     <row r="22" spans="2:16" ht="19.5" customHeight="1">
       <c r="B22" s="37"/>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="80"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="57" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,12,0)</f>
-        <v>El aplicativo muestra un mensaje de confirmación para eliminar  la orden de trabajo</v>
-      </c>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,12,0)</f>
+        <v>El aplicativo muestra el reporte de la fecha seleccionada</v>
+      </c>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="59"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="56" t="s">
+      <c r="J22" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="K22" s="80"/>
-      <c r="L22" s="59" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O19,13,0)</f>
+      <c r="K22" s="51"/>
+      <c r="L22" s="71" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O20,13,0)</f>
         <v>N/A</v>
       </c>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="80"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="51"/>
       <c r="P22" s="38"/>
     </row>
     <row r="23" spans="2:16" ht="19.5" customHeight="1">
       <c r="B23" s="37"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="48"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="62"/>
       <c r="I23" s="6"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="90"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="56"/>
       <c r="P23" s="38"/>
     </row>
     <row r="24" spans="2:16" ht="19.5" customHeight="1">
       <c r="B24" s="37"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="65"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="84"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="53"/>
       <c r="P24" s="38"/>
     </row>
     <row r="25" spans="2:16" ht="9.75" customHeight="1">
@@ -9237,6 +9313,11 @@
     <row r="1020" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="M15:O17"/>
+    <mergeCell ref="E19:O20"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="C19:D20"/>
     <mergeCell ref="C22:D24"/>
@@ -9253,11 +9334,6 @@
     <mergeCell ref="D15:E17"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="H15:J17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="M15:O17"/>
-    <mergeCell ref="E19:O20"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I11">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -9282,7 +9358,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>'Formato descripción HU'!$B$6:$B$19</xm:f>
+            <xm:f>'Formato descripción HU'!$B$6:$B$20</xm:f>
           </x14:formula1>
           <xm:sqref>C10:C11</xm:sqref>
         </x14:dataValidation>
@@ -9293,20 +9369,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f1f31ffb-9912-4459-99c8-b26e82094b51" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f1f31ffb-9912-4459-99c8-b26e82094b51" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9505,13 +9581,38 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B92EABA-029D-4E15-9CAD-35D85D8AFEB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BB9B8E-F37C-4883-BB4F-987669CAAE30}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BB9B8E-F37C-4883-BB4F-987669CAAE30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B92EABA-029D-4E15-9CAD-35D85D8AFEB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E2F3D1-C235-4C14-B824-1A8C3F52885C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E2F3D1-C235-4C14-B824-1A8C3F52885C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f1f31ffb-9912-4459-99c8-b26e82094b51"/>
+    <ds:schemaRef ds:uri="ce621958-37b1-43fe-a1f1-1aad67996a88"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>